--- a/excel/Plantilla-Items.xlsx
+++ b/excel/Plantilla-Items.xlsx
@@ -8,8 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\github\apiPOS-Official\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50078B6B-5B39-4F5B-B582-60264469826E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="hhOzpNyo3JCWR9/uzi4PW2gPh3gFfTVeXBr6Ae5RYPA4+Qv2CbQp2gS6x+YhTaxyQo9LPcwbFXmVpydpQ1zeNg==" workbookSaltValue="QhDUFpAiWiHQWUkpC4dYnw==" workbookSpinCount="100000" lockStructure="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61E4396B-31EE-44F0-94E9-A743DA88BCC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5647" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5649" uniqueCount="167">
   <si>
     <t>Tipo*</t>
   </si>
@@ -523,6 +522,12 @@
   <si>
     <t>Img 4</t>
   </si>
+  <si>
+    <t>Gravado (10.5%)</t>
+  </si>
+  <si>
+    <t>Gravado Gratuito (10.5%)</t>
+  </si>
 </sst>
 </file>
 
@@ -1012,8 +1017,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A4117193-5232-4FAA-8343-84B5AA251D48}" name="Impuesto" displayName="Impuesto" ref="B1:B10" totalsRowShown="0" headerRowDxfId="7">
-  <autoFilter ref="B1:B10" xr:uid="{A4117193-5232-4FAA-8343-84B5AA251D48}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A4117193-5232-4FAA-8343-84B5AA251D48}" name="Impuesto" displayName="Impuesto" ref="B1:B12" totalsRowShown="0" headerRowDxfId="7">
+  <autoFilter ref="B1:B12" xr:uid="{A4117193-5232-4FAA-8343-84B5AA251D48}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{F1397571-8E9F-4654-A7B2-9A56E9C31FE4}" name="Impuesto*"/>
   </tableColumns>
@@ -1327,7 +1332,7 @@
     <col min="8" max="8" width="17" customWidth="1"/>
     <col min="9" max="9" width="16.140625" customWidth="1"/>
     <col min="10" max="10" width="14.42578125" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="23.85546875" customWidth="1"/>
     <col min="12" max="15" width="16.7109375" customWidth="1"/>
     <col min="16" max="16" width="15.5703125" customWidth="1"/>
     <col min="17" max="17" width="20.140625" customWidth="1"/>
@@ -56045,6 +56050,7 @@
       <c r="R507" s="2"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="OSUaKiD4nV6VWYL2kSlAHB9dkzLMUJYDVbpYWAZobuQJZvZqdikICorsy/mxIXlEe7++Z1dIMtoksNwy6vttdQ==" saltValue="ZcJD03ymyBRQtE19LUr17A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="8">
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="BT1:BU1"/>
@@ -56059,12 +56065,12 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EBC0BBAB-6A9B-4220-91D8-35D65D3BC73C}">
           <x14:formula1>
             <xm:f>Config!$B$2:$B$10</xm:f>
           </x14:formula1>
-          <xm:sqref>K3:K500 S3:S500</xm:sqref>
+          <xm:sqref>S3:S500</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C555FE2D-31E0-441C-96DF-0242BC66E17F}">
           <x14:formula1>
@@ -56090,6 +56096,12 @@
           </x14:formula1>
           <xm:sqref>B3:B500</xm:sqref>
         </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5D34F53B-8DFE-4C48-8B25-8BE48B39BDC1}">
+          <x14:formula1>
+            <xm:f>Config!$B$2:$B$12</xm:f>
+          </x14:formula1>
+          <xm:sqref>K3:K500</xm:sqref>
+        </x14:dataValidation>
       </x14:dataValidations>
     </ext>
   </extLst>
@@ -56228,11 +56240,17 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>165</v>
+      </c>
       <c r="C11" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>166</v>
+      </c>
       <c r="C12" t="s">
         <v>67</v>
       </c>
@@ -56503,7 +56521,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="xtRcOCA7pze4VUk+z+Unye+YCtfLcHJJX55eCKeUJCnqP/OQt+B/tcj2235jP7WP+k0ovXi8cOBbM21NkSA4kw==" saltValue="d1a6YIMEDHZwU88ZFlchOA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="tCgQ82qxf9XpgGQPWgPWO/1LlUkRW6WBNc5zV9hQnZzjVnHuatN6XMSWVNK4tq65tuwdtKeFEiydLFCNlQSEKA==" saltValue="GIJKJNIWYGXq5Npm7H5OqQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="5">

--- a/excel/Plantilla-Items.xlsx
+++ b/excel/Plantilla-Items.xlsx
@@ -8,7 +8,8 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\github\apiPOS-Official\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61E4396B-31EE-44F0-94E9-A743DA88BCC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D562A9A7-30C7-482C-BAF9-847CF50367C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="Fk2aU5PIdPDuNBuWJXkekJbb2gcqIDnBwztH3OqFKbv0igA21aMmYjsNmSmKpRwhsiozqy1mnRzEeTYuJ0NJSQ==" workbookSaltValue="K5p4jYkf0GEgeFgqviALig==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56050,7 +56051,6 @@
       <c r="R507" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="OSUaKiD4nV6VWYL2kSlAHB9dkzLMUJYDVbpYWAZobuQJZvZqdikICorsy/mxIXlEe7++Z1dIMtoksNwy6vttdQ==" saltValue="ZcJD03ymyBRQtE19LUr17A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="8">
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="BT1:BU1"/>
